--- a/output/details/2025-05-31/nowcast_output.xlsx
+++ b/output/details/2025-05-31/nowcast_output.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.9942</v>
+        <v>0.9953</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9942</v>
+        <v>0.9953</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0058</v>
+        <v>0.0047</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.9952</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.9952</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0055</v>
+        <v>0.0048</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9986</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -966,13 +966,13 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0014</v>
+        <v>0.0015</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9986</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9997</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.0005</v>
+        <v>0.0003</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9997</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.9921</v>
+        <v>0.9928</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.0018</v>
+        <v>0.0011</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9921</v>
+        <v>0.9928</v>
       </c>
       <c r="J20" t="n">
         <v>0.0061</v>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.7827</v>
+        <v>0.7745</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.7827</v>
+        <v>0.7745</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2173</v>
+        <v>0.2255</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0.9895</v>
+        <v>0.9908</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.9895</v>
+        <v>0.9908</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0105</v>
+        <v>0.0092</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3290,13 +3290,13 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0.7768</v>
+        <v>0.7813</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3417,16 +3417,16 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.2115</v>
+        <v>0.2067</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0117</v>
+        <v>0.012</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0.7768</v>
+        <v>0.7813</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0.9999</v>
+        <v>0.9996</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.0001</v>
+        <v>0.0004</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>0.9999</v>
+        <v>0.9996</v>
       </c>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.999</v>
+        <v>0.9993</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.001</v>
+        <v>0.0007</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -3816,7 +3816,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0.999</v>
+        <v>0.9993</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.8808</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.1192</v>
+        <v>0.1195</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>0.8808</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5591</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4720,13 +4720,13 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>0.434</v>
+        <v>0.4409</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5591</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.9953</v>
+        <v>0.9966</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.0047</v>
+        <v>0.0034</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -4921,7 +4921,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0.9953</v>
+        <v>0.9966</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.767</v>
+        <v>0.7724</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.767</v>
+        <v>0.7724</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -4986,7 +4986,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0.233</v>
+        <v>0.2276</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9979</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -5237,16 +5237,16 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9979</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0032</v>
+        <v>0.002</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0.9959</v>
+        <v>0.9954</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -5302,10 +5302,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.0041</v>
+        <v>0.0046</v>
       </c>
       <c r="I75" t="n">
-        <v>0.9959</v>
+        <v>0.9954</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0.8215</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.8215</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
@@ -5518,7 +5518,7 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>0.1785</v>
+        <v>0.1779</v>
       </c>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
@@ -5554,7 +5554,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -5565,13 +5565,13 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5890,13 +5890,13 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -5940,11 +5940,11 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>0.501</v>
+        <v>0.5026</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0.501</v>
+        <v>0.4974</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
@@ -5961,7 +5961,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.499</v>
+        <v>0.5026</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -6150,13 +6150,13 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0.8044</v>
+        <v>0.8115</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>0.8044</v>
+        <v>0.8115</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
@@ -6419,7 +6419,7 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0.1956</v>
+        <v>0.1885</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -6670,13 +6670,13 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0.9767</v>
+        <v>0.9795</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -6800,13 +6800,13 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9767</v>
+        <v>0.9795</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0.0233</v>
+        <v>0.0205</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0.9691</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>0.0309</v>
+        <v>0.0318</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
@@ -6936,7 +6936,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0.9691</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0.6684</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>0.6684</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>0.3316</v>
+        <v>0.3443</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0.6459</v>
+        <v>0.6428</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -7320,13 +7320,13 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>0.3541</v>
+        <v>0.3572</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>0.6459</v>
+        <v>0.6428</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>0.9928</v>
+        <v>0.9932</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>0.9928</v>
+        <v>0.9932</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
@@ -7651,7 +7651,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>0.0072</v>
+        <v>0.0068</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -8154,7 +8154,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>0.9822</v>
+        <v>0.9817</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>0.0178</v>
+        <v>0.0183</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>0.9822</v>
+        <v>0.9817</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>0.9776</v>
+        <v>0.9799</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>0.9776</v>
+        <v>0.9799</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>0.0224</v>
+        <v>0.0201</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.5836</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -8812,10 +8812,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>0.4209</v>
+        <v>0.4164</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.5836</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.9213</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>0.0771</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
@@ -9146,7 +9146,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.9213</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>0.9754</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>0.9754</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
@@ -9666,7 +9666,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>0.0246</v>
+        <v>0.0227</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -9909,7 +9909,7 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9643</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9643</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0328</v>
+        <v>0.0357</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -9974,7 +9974,7 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.8983</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.8983</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>0.1023</v>
+        <v>0.1017</v>
       </c>
       <c r="N147" t="n">
         <v>0</v>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -10112,10 +10112,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -10169,7 +10169,7 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>0.954</v>
+        <v>0.9523</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -10177,10 +10177,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>0.046</v>
+        <v>0.0477</v>
       </c>
       <c r="I150" t="n">
-        <v>0.954</v>
+        <v>0.9523</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -10364,7 +10364,7 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>0.9191</v>
+        <v>0.9215</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>0.9191</v>
+        <v>0.9215</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>0.0809</v>
+        <v>0.0785</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -10559,7 +10559,7 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>0.8957000000000001</v>
+        <v>0.8942</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>0.1043</v>
+        <v>0.1058</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
@@ -10576,7 +10576,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>0.8957000000000001</v>
+        <v>0.8942</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -10689,7 +10689,7 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>0.8699</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>0.8699</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
@@ -10706,7 +10706,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>0.1301</v>
+        <v>0.1235</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -11014,7 +11014,7 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>0.9444</v>
+        <v>0.9476</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>0.9444</v>
+        <v>0.9476</v>
       </c>
       <c r="I163" t="n">
         <v>0</v>
@@ -11031,7 +11031,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>0.0556</v>
+        <v>0.0524</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -11079,7 +11079,7 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>0.8164</v>
+        <v>0.8145</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -11087,16 +11087,16 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>0.8164</v>
+        <v>0.8145</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1829</v>
+        <v>0.1851</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>0.0007</v>
+        <v>0.0004</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -11144,7 +11144,7 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>0.9493</v>
+        <v>0.9468</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -11155,13 +11155,13 @@
         <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0507</v>
+        <v>0.0532</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>0.9493</v>
+        <v>0.9468</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>0.7003</v>
+        <v>0.7075</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -11220,13 +11220,13 @@
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>0.7003</v>
+        <v>0.7075</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>0.2997</v>
+        <v>0.2925</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -11274,7 +11274,7 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>0.8849</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>0.8849</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
@@ -11291,7 +11291,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>0.1151</v>
+        <v>0.1114</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -12184,7 +12184,7 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>0.8806</v>
+        <v>0.883</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>0.8806</v>
+        <v>0.883</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -12207,7 +12207,7 @@
         <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>0.1194</v>
+        <v>0.117</v>
       </c>
       <c r="N181" t="n">
         <v>0</v>
@@ -12314,15 +12314,15 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>0.9477</v>
+        <v>0.9502</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Likely Labour</t>
+          <t>Safe Labour</t>
         </is>
       </c>
       <c r="H183" t="n">
-        <v>0.9477</v>
+        <v>0.9502</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
@@ -12337,7 +12337,7 @@
         <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>0.0523</v>
+        <v>0.0498</v>
       </c>
       <c r="N183" t="n">
         <v>0</v>
@@ -12379,7 +12379,7 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>0.8257</v>
+        <v>0.8269</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -12390,13 +12390,13 @@
         <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>0.8257</v>
+        <v>0.8269</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>0.1743</v>
+        <v>0.1731</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -12704,7 +12704,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>0.9644</v>
+        <v>0.963</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -12712,10 +12712,10 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>0.0356</v>
+        <v>0.037</v>
       </c>
       <c r="I189" t="n">
-        <v>0.9644</v>
+        <v>0.963</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>0.9129</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -13036,10 +13036,10 @@
         <v>0</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0871</v>
+        <v>0.0862</v>
       </c>
       <c r="J194" t="n">
-        <v>0.9129</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="K194" t="n">
         <v>0</v>
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>0.7592</v>
+        <v>0.7648</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>0.7592</v>
+        <v>0.7648</v>
       </c>
       <c r="I195" t="n">
         <v>0</v>
@@ -13113,7 +13113,7 @@
         <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>0.2408</v>
+        <v>0.2352</v>
       </c>
       <c r="N195" t="n">
         <v>0</v>
@@ -13736,7 +13736,7 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>0.763</v>
+        <v>0.7635</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>0.237</v>
+        <v>0.2365</v>
       </c>
       <c r="I205" t="n">
         <v>0</v>
@@ -13759,7 +13759,7 @@
         <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>0.763</v>
+        <v>0.7635</v>
       </c>
       <c r="N205" t="n">
         <v>0</v>
@@ -14711,7 +14711,7 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -14722,13 +14722,13 @@
         <v>0</v>
       </c>
       <c r="I220" t="n">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
       </c>
       <c r="K220" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="L220" t="n">
         <v>0</v>
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>0.6441</v>
+        <v>0.6483</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -14982,13 +14982,13 @@
         <v>0</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6441</v>
+        <v>0.6483</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
       </c>
       <c r="K224" t="n">
-        <v>0.3559</v>
+        <v>0.3517</v>
       </c>
       <c r="L224" t="n">
         <v>0</v>
@@ -15357,7 +15357,7 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -15368,13 +15368,13 @@
         <v>0</v>
       </c>
       <c r="I230" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
       </c>
       <c r="K230" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="L230" t="n">
         <v>0</v>
@@ -15613,7 +15613,7 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>0.5938</v>
+        <v>0.5846</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -15624,13 +15624,13 @@
         <v>0</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4062</v>
+        <v>0.4154</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
       </c>
       <c r="K234" t="n">
-        <v>0.5938</v>
+        <v>0.5846</v>
       </c>
       <c r="L234" t="n">
         <v>0</v>
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>0.996</v>
+        <v>0.9973</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>0.004</v>
+        <v>0.0027</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
@@ -15695,7 +15695,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="n">
-        <v>0.996</v>
+        <v>0.9973</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -15808,7 +15808,7 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9997</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>0.0005</v>
+        <v>0.0003</v>
       </c>
       <c r="I237" t="n">
         <v>0</v>
@@ -15825,7 +15825,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9997</v>
       </c>
       <c r="L237" t="n">
         <v>0</v>
@@ -15873,7 +15873,7 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>0.9969</v>
+        <v>0.9983</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>0.0031</v>
+        <v>0.0017</v>
       </c>
       <c r="I238" t="n">
         <v>0</v>
@@ -15896,7 +15896,7 @@
         <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>0.9969</v>
+        <v>0.9983</v>
       </c>
       <c r="N238" t="n">
         <v>0</v>
@@ -15938,7 +15938,7 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>0.9903</v>
+        <v>0.99</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         </is>
       </c>
       <c r="H239" t="n">
-        <v>0.0097</v>
+        <v>0.01</v>
       </c>
       <c r="I239" t="n">
         <v>0</v>
@@ -15961,7 +15961,7 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>0.9903</v>
+        <v>0.99</v>
       </c>
       <c r="N239" t="n">
         <v>0</v>
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>0.6243</v>
+        <v>0.6238</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>0.6243</v>
+        <v>0.6238</v>
       </c>
       <c r="I240" t="n">
         <v>0</v>
@@ -16026,7 +16026,7 @@
         <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>0.3757</v>
+        <v>0.3762</v>
       </c>
       <c r="N240" t="n">
         <v>0</v>
@@ -16133,7 +16133,7 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9999</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>0.0005</v>
+        <v>0.0001</v>
       </c>
       <c r="I242" t="n">
         <v>0</v>
@@ -16156,7 +16156,7 @@
         <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9999</v>
       </c>
       <c r="N242" t="n">
         <v>0</v>
@@ -16198,7 +16198,7 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6892</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>0.317</v>
+        <v>0.3108</v>
       </c>
       <c r="I243" t="n">
         <v>0</v>
@@ -16221,7 +16221,7 @@
         <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6892</v>
       </c>
       <c r="N243" t="n">
         <v>0</v>
@@ -16393,7 +16393,7 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9991</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -16401,10 +16401,10 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9991</v>
       </c>
       <c r="I246" t="n">
-        <v>0.0015</v>
+        <v>0.0009</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -16848,7 +16848,7 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>0.9888</v>
+        <v>0.9898</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
@@ -16859,13 +16859,13 @@
         <v>0</v>
       </c>
       <c r="I253" t="n">
-        <v>0.9888</v>
+        <v>0.9898</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
       </c>
       <c r="K253" t="n">
-        <v>0.0112</v>
+        <v>0.0102</v>
       </c>
       <c r="L253" t="n">
         <v>0</v>
@@ -16909,11 +16909,11 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>0.4001</v>
+        <v>0.3977</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -16921,16 +16921,16 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>0.4001</v>
+        <v>0.3919</v>
       </c>
       <c r="I254" t="n">
-        <v>0.3877</v>
+        <v>0.3977</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
       </c>
       <c r="K254" t="n">
-        <v>0.2122</v>
+        <v>0.2104</v>
       </c>
       <c r="L254" t="n">
         <v>0</v>
@@ -18213,7 +18213,7 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>0.7814</v>
+        <v>0.7788</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -18224,13 +18224,13 @@
         <v>0</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2186</v>
+        <v>0.2212</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
       </c>
       <c r="K274" t="n">
-        <v>0.7814</v>
+        <v>0.7788</v>
       </c>
       <c r="L274" t="n">
         <v>0</v>
@@ -18343,7 +18343,7 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -18354,13 +18354,13 @@
         <v>0</v>
       </c>
       <c r="I276" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
       </c>
       <c r="K276" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="L276" t="n">
         <v>0</v>
@@ -18538,7 +18538,7 @@
         </is>
       </c>
       <c r="F279" t="n">
-        <v>0.8868</v>
+        <v>0.8867</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>0.1132</v>
+        <v>0.1133</v>
       </c>
       <c r="I279" t="n">
         <v>0</v>
@@ -18555,7 +18555,7 @@
         <v>0</v>
       </c>
       <c r="K279" t="n">
-        <v>0.8868</v>
+        <v>0.8867</v>
       </c>
       <c r="L279" t="n">
         <v>0</v>
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="F280" t="n">
-        <v>0.9875</v>
+        <v>0.9878</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -18611,10 +18611,10 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>0.9875</v>
+        <v>0.9878</v>
       </c>
       <c r="I280" t="n">
-        <v>0.0125</v>
+        <v>0.0122</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>0.9778</v>
+        <v>0.9801</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
@@ -18744,13 +18744,13 @@
         <v>0</v>
       </c>
       <c r="I282" t="n">
-        <v>0.9778</v>
+        <v>0.9801</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
       </c>
       <c r="K282" t="n">
-        <v>0.0222</v>
+        <v>0.0199</v>
       </c>
       <c r="L282" t="n">
         <v>0</v>
@@ -18798,7 +18798,7 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>0.9994</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
@@ -18809,13 +18809,13 @@
         <v>0</v>
       </c>
       <c r="I283" t="n">
-        <v>0.9994</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
       </c>
       <c r="K283" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0005</v>
       </c>
       <c r="L283" t="n">
         <v>0</v>
@@ -18863,7 +18863,7 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>0.5284</v>
+        <v>0.5375</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
@@ -18871,16 +18871,16 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>0.4713</v>
+        <v>0.4624</v>
       </c>
       <c r="I284" t="n">
-        <v>0.5284</v>
+        <v>0.5375</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
       </c>
       <c r="K284" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="L284" t="n">
         <v>0</v>
@@ -18993,7 +18993,7 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>0.7645</v>
+        <v>0.7625</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -19001,10 +19001,10 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>0.2355</v>
+        <v>0.2375</v>
       </c>
       <c r="I286" t="n">
-        <v>0.7645</v>
+        <v>0.7625</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -19773,7 +19773,7 @@
         </is>
       </c>
       <c r="F298" t="n">
-        <v>0.9336</v>
+        <v>0.9387</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>0.9336</v>
+        <v>0.9387</v>
       </c>
       <c r="I298" t="n">
         <v>0</v>
@@ -19793,7 +19793,7 @@
         <v>0</v>
       </c>
       <c r="L298" t="n">
-        <v>0.0664</v>
+        <v>0.0613</v>
       </c>
       <c r="M298" t="n">
         <v>0</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="F303" t="n">
-        <v>0.7446</v>
+        <v>0.7477</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         </is>
       </c>
       <c r="H303" t="n">
-        <v>0.2554</v>
+        <v>0.2523</v>
       </c>
       <c r="I303" t="n">
         <v>0</v>
@@ -20121,7 +20121,7 @@
         <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>0.7446</v>
+        <v>0.7477</v>
       </c>
       <c r="N303" t="n">
         <v>0</v>
@@ -20163,7 +20163,7 @@
         </is>
       </c>
       <c r="F304" t="n">
-        <v>0.8124</v>
+        <v>0.8119</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>0</v>
       </c>
       <c r="J304" t="n">
-        <v>0.1876</v>
+        <v>0.1881</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
@@ -20186,7 +20186,7 @@
         <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>0.8124</v>
+        <v>0.8119</v>
       </c>
       <c r="N304" t="n">
         <v>0</v>
@@ -20293,7 +20293,7 @@
         </is>
       </c>
       <c r="F306" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
@@ -20304,13 +20304,13 @@
         <v>0</v>
       </c>
       <c r="I306" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="J306" t="n">
         <v>0</v>
       </c>
       <c r="K306" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="L306" t="n">
         <v>0</v>
@@ -20358,7 +20358,7 @@
         </is>
       </c>
       <c r="F307" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9971</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
@@ -20366,16 +20366,16 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9971</v>
       </c>
       <c r="I307" t="n">
-        <v>0.0023</v>
+        <v>0.0018</v>
       </c>
       <c r="J307" t="n">
         <v>0</v>
       </c>
       <c r="K307" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="L307" t="n">
         <v>0</v>
@@ -20813,7 +20813,7 @@
         </is>
       </c>
       <c r="F314" t="n">
-        <v>0.989</v>
+        <v>0.9898</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -20821,16 +20821,16 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>0.0007</v>
+        <v>0.0005</v>
       </c>
       <c r="I314" t="n">
-        <v>0.0103</v>
+        <v>0.0097</v>
       </c>
       <c r="J314" t="n">
         <v>0</v>
       </c>
       <c r="K314" t="n">
-        <v>0.989</v>
+        <v>0.9898</v>
       </c>
       <c r="L314" t="n">
         <v>0</v>
@@ -21073,7 +21073,7 @@
         </is>
       </c>
       <c r="F318" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8891</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>0.1104</v>
+        <v>0.1109</v>
       </c>
       <c r="I318" t="n">
         <v>0</v>
@@ -21090,7 +21090,7 @@
         <v>0</v>
       </c>
       <c r="K318" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8891</v>
       </c>
       <c r="L318" t="n">
         <v>0</v>
@@ -21333,7 +21333,7 @@
         </is>
       </c>
       <c r="F322" t="n">
-        <v>0.9857</v>
+        <v>0.9862</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
@@ -21349,13 +21349,13 @@
       <c r="N322" t="inlineStr"/>
       <c r="O322" t="inlineStr"/>
       <c r="P322" t="n">
-        <v>0.0143</v>
+        <v>0.0138</v>
       </c>
       <c r="Q322" t="n">
         <v>0</v>
       </c>
       <c r="R322" t="n">
-        <v>0.9857</v>
+        <v>0.9862</v>
       </c>
       <c r="S322" t="n">
         <v>0</v>
@@ -21524,7 +21524,7 @@
         </is>
       </c>
       <c r="F325" t="n">
-        <v>0.9986</v>
+        <v>0.9992</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>0.9986</v>
+        <v>0.9992</v>
       </c>
       <c r="I325" t="n">
         <v>0</v>
@@ -21541,7 +21541,7 @@
         <v>0</v>
       </c>
       <c r="K325" t="n">
-        <v>0.0014</v>
+        <v>0.0008</v>
       </c>
       <c r="L325" t="n">
         <v>0</v>
@@ -21784,7 +21784,7 @@
         </is>
       </c>
       <c r="F329" t="n">
-        <v>0.9928</v>
+        <v>0.994</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>0.0072</v>
+        <v>0.006</v>
       </c>
       <c r="I329" t="n">
         <v>0</v>
@@ -21801,7 +21801,7 @@
         <v>0</v>
       </c>
       <c r="K329" t="n">
-        <v>0.9928</v>
+        <v>0.994</v>
       </c>
       <c r="L329" t="n">
         <v>0</v>
@@ -21979,7 +21979,7 @@
         </is>
       </c>
       <c r="F332" t="n">
-        <v>0.6819</v>
+        <v>0.6832</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>0.3181</v>
+        <v>0.3168</v>
       </c>
       <c r="I332" t="n">
         <v>0</v>
@@ -22008,7 +22008,7 @@
         <v>0</v>
       </c>
       <c r="O332" t="n">
-        <v>0.6819</v>
+        <v>0.6832</v>
       </c>
       <c r="P332" t="inlineStr"/>
       <c r="Q332" t="inlineStr"/>
@@ -22499,7 +22499,7 @@
         </is>
       </c>
       <c r="F340" t="n">
-        <v>0.9849</v>
+        <v>0.9863</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
@@ -22510,13 +22510,13 @@
         <v>0</v>
       </c>
       <c r="I340" t="n">
-        <v>0.0151</v>
+        <v>0.0137</v>
       </c>
       <c r="J340" t="n">
         <v>0</v>
       </c>
       <c r="K340" t="n">
-        <v>0.9849</v>
+        <v>0.9863</v>
       </c>
       <c r="L340" t="n">
         <v>0</v>
@@ -22564,7 +22564,7 @@
         </is>
       </c>
       <c r="F341" t="n">
-        <v>0.9716</v>
+        <v>0.9729</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>0.9716</v>
+        <v>0.9729</v>
       </c>
       <c r="I341" t="n">
         <v>0</v>
@@ -22581,7 +22581,7 @@
         <v>0</v>
       </c>
       <c r="K341" t="n">
-        <v>0.0284</v>
+        <v>0.0271</v>
       </c>
       <c r="L341" t="n">
         <v>0</v>
@@ -23149,7 +23149,7 @@
         </is>
       </c>
       <c r="F350" t="n">
-        <v>0.9997</v>
+        <v>0.9999</v>
       </c>
       <c r="G350" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>0.9997</v>
+        <v>0.9999</v>
       </c>
       <c r="I350" t="n">
         <v>0</v>
@@ -23166,7 +23166,7 @@
         <v>0</v>
       </c>
       <c r="K350" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="L350" t="n">
         <v>0</v>
@@ -23409,7 +23409,7 @@
         </is>
       </c>
       <c r="F354" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="G354" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="I354" t="n">
         <v>0</v>
@@ -23438,7 +23438,7 @@
         <v>0</v>
       </c>
       <c r="O354" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="P354" t="inlineStr"/>
       <c r="Q354" t="inlineStr"/>
@@ -23604,7 +23604,7 @@
         </is>
       </c>
       <c r="F357" t="n">
-        <v>0.743</v>
+        <v>0.7493</v>
       </c>
       <c r="G357" t="inlineStr">
         <is>
@@ -23615,13 +23615,13 @@
         <v>0</v>
       </c>
       <c r="I357" t="n">
-        <v>0.743</v>
+        <v>0.7493</v>
       </c>
       <c r="J357" t="n">
         <v>0</v>
       </c>
       <c r="K357" t="n">
-        <v>0.257</v>
+        <v>0.2507</v>
       </c>
       <c r="L357" t="n">
         <v>0</v>
@@ -23734,7 +23734,7 @@
         </is>
       </c>
       <c r="F359" t="n">
-        <v>0.9374</v>
+        <v>0.9351</v>
       </c>
       <c r="G359" t="inlineStr">
         <is>
@@ -23745,13 +23745,13 @@
         <v>0</v>
       </c>
       <c r="I359" t="n">
-        <v>0.0626</v>
+        <v>0.0649</v>
       </c>
       <c r="J359" t="n">
         <v>0</v>
       </c>
       <c r="K359" t="n">
-        <v>0.9374</v>
+        <v>0.9351</v>
       </c>
       <c r="L359" t="n">
         <v>0</v>
@@ -24189,7 +24189,7 @@
         </is>
       </c>
       <c r="F366" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
@@ -24200,13 +24200,13 @@
         <v>0</v>
       </c>
       <c r="I366" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="J366" t="n">
         <v>0</v>
       </c>
       <c r="K366" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="L366" t="n">
         <v>0</v>
@@ -24319,7 +24319,7 @@
         </is>
       </c>
       <c r="F368" t="n">
-        <v>0.908</v>
+        <v>0.9079</v>
       </c>
       <c r="G368" t="inlineStr">
         <is>
@@ -24327,10 +24327,10 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>0.908</v>
+        <v>0.9079</v>
       </c>
       <c r="I368" t="n">
-        <v>0.092</v>
+        <v>0.0921</v>
       </c>
       <c r="J368" t="n">
         <v>0</v>
@@ -24587,7 +24587,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="I372" t="n">
         <v>0.924</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="K372" t="n">
-        <v>0.0759</v>
+        <v>0.076</v>
       </c>
       <c r="L372" t="n">
         <v>0</v>
@@ -24839,7 +24839,7 @@
         </is>
       </c>
       <c r="F376" t="n">
-        <v>0.9879</v>
+        <v>0.9885</v>
       </c>
       <c r="G376" t="inlineStr">
         <is>
@@ -24850,13 +24850,13 @@
         <v>0</v>
       </c>
       <c r="I376" t="n">
-        <v>0.9879</v>
+        <v>0.9885</v>
       </c>
       <c r="J376" t="n">
         <v>0</v>
       </c>
       <c r="K376" t="n">
-        <v>0.0121</v>
+        <v>0.0115</v>
       </c>
       <c r="L376" t="n">
         <v>0</v>
@@ -25030,7 +25030,7 @@
         </is>
       </c>
       <c r="F379" t="n">
-        <v>0.9821</v>
+        <v>0.982</v>
       </c>
       <c r="G379" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>0.0179</v>
+        <v>0.018</v>
       </c>
       <c r="I379" t="n">
         <v>0</v>
@@ -25047,7 +25047,7 @@
         <v>0</v>
       </c>
       <c r="K379" t="n">
-        <v>0.9821</v>
+        <v>0.982</v>
       </c>
       <c r="L379" t="n">
         <v>0</v>
@@ -25095,7 +25095,7 @@
         </is>
       </c>
       <c r="F380" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G380" t="inlineStr">
         <is>
@@ -25103,10 +25103,10 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="I380" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="J380" t="n">
         <v>0</v>
@@ -25160,7 +25160,7 @@
         </is>
       </c>
       <c r="F381" t="n">
-        <v>0.9982</v>
+        <v>0.9979</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>0.9982</v>
+        <v>0.9979</v>
       </c>
       <c r="I381" t="n">
         <v>0</v>
@@ -25183,7 +25183,7 @@
         <v>0</v>
       </c>
       <c r="M381" t="n">
-        <v>0.0018</v>
+        <v>0.0021</v>
       </c>
       <c r="N381" t="n">
         <v>0</v>
@@ -25420,7 +25420,7 @@
         </is>
       </c>
       <c r="F385" t="n">
-        <v>0.8225</v>
+        <v>0.8227</v>
       </c>
       <c r="G385" t="inlineStr">
         <is>
@@ -25428,10 +25428,10 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>0.8225</v>
+        <v>0.8227</v>
       </c>
       <c r="I385" t="n">
-        <v>0.1775</v>
+        <v>0.1773</v>
       </c>
       <c r="J385" t="n">
         <v>0</v>
@@ -25615,7 +25615,7 @@
         </is>
       </c>
       <c r="F388" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
@@ -25623,10 +25623,10 @@
         </is>
       </c>
       <c r="H388" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="I388" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="J388" t="n">
         <v>0</v>
@@ -25680,7 +25680,7 @@
         </is>
       </c>
       <c r="F389" t="n">
-        <v>0.8757</v>
+        <v>0.8758</v>
       </c>
       <c r="G389" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>0.8757</v>
+        <v>0.8758</v>
       </c>
       <c r="I389" t="n">
         <v>0</v>
@@ -25703,7 +25703,7 @@
         <v>0</v>
       </c>
       <c r="M389" t="n">
-        <v>0.1243</v>
+        <v>0.1242</v>
       </c>
       <c r="N389" t="n">
         <v>0</v>
@@ -26135,7 +26135,7 @@
         </is>
       </c>
       <c r="F396" t="n">
-        <v>0.995</v>
+        <v>0.9959</v>
       </c>
       <c r="G396" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>0.995</v>
+        <v>0.9959</v>
       </c>
       <c r="I396" t="n">
         <v>0</v>
@@ -26152,7 +26152,7 @@
         <v>0</v>
       </c>
       <c r="K396" t="n">
-        <v>0.005</v>
+        <v>0.0041</v>
       </c>
       <c r="L396" t="n">
         <v>0</v>
@@ -26395,7 +26395,7 @@
         </is>
       </c>
       <c r="F400" t="n">
-        <v>0.9953</v>
+        <v>0.9963</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>0.9953</v>
+        <v>0.9963</v>
       </c>
       <c r="I400" t="n">
         <v>0</v>
@@ -26412,7 +26412,7 @@
         <v>0</v>
       </c>
       <c r="K400" t="n">
-        <v>0.0047</v>
+        <v>0.0037</v>
       </c>
       <c r="L400" t="n">
         <v>0</v>
@@ -26460,7 +26460,7 @@
         </is>
       </c>
       <c r="F401" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.9913</v>
       </c>
       <c r="G401" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         </is>
       </c>
       <c r="H401" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="I401" t="n">
         <v>0</v>
@@ -26477,7 +26477,7 @@
         <v>0</v>
       </c>
       <c r="K401" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.9913</v>
       </c>
       <c r="L401" t="n">
         <v>0</v>
@@ -27167,7 +27167,7 @@
         </is>
       </c>
       <c r="F412" t="n">
-        <v>0.7528</v>
+        <v>0.7552</v>
       </c>
       <c r="G412" t="inlineStr">
         <is>
@@ -27178,10 +27178,10 @@
         <v>0</v>
       </c>
       <c r="I412" t="n">
-        <v>0.7528</v>
+        <v>0.7552</v>
       </c>
       <c r="J412" t="n">
-        <v>0.2472</v>
+        <v>0.2448</v>
       </c>
       <c r="K412" t="n">
         <v>0</v>
@@ -27358,7 +27358,7 @@
         </is>
       </c>
       <c r="F415" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G415" t="inlineStr">
         <is>
@@ -27369,13 +27369,13 @@
         <v>0</v>
       </c>
       <c r="I415" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="J415" t="n">
         <v>0</v>
       </c>
       <c r="K415" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="L415" t="n">
         <v>0</v>
@@ -27423,7 +27423,7 @@
         </is>
       </c>
       <c r="F416" t="n">
-        <v>0.9918</v>
+        <v>0.9903</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
@@ -27431,16 +27431,16 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="I416" t="n">
-        <v>0.9918</v>
+        <v>0.9903</v>
       </c>
       <c r="J416" t="n">
         <v>0</v>
       </c>
       <c r="K416" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="L416" t="n">
         <v>0</v>
@@ -27618,7 +27618,7 @@
         </is>
       </c>
       <c r="F419" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="G419" t="inlineStr">
         <is>
@@ -27626,16 +27626,16 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="I419" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="J419" t="n">
         <v>0</v>
       </c>
       <c r="K419" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="L419" t="n">
         <v>0</v>
@@ -27683,7 +27683,7 @@
         </is>
       </c>
       <c r="F420" t="n">
-        <v>0.9865</v>
+        <v>0.9871</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
@@ -27691,10 +27691,10 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>0.9865</v>
+        <v>0.9871</v>
       </c>
       <c r="I420" t="n">
-        <v>0.0135</v>
+        <v>0.0129</v>
       </c>
       <c r="J420" t="n">
         <v>0</v>
@@ -27878,7 +27878,7 @@
         </is>
       </c>
       <c r="F423" t="n">
-        <v>0.6019</v>
+        <v>0.6049</v>
       </c>
       <c r="G423" t="inlineStr">
         <is>
@@ -27886,16 +27886,16 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>0.3599</v>
+        <v>0.3539</v>
       </c>
       <c r="I423" t="n">
-        <v>0.0382</v>
+        <v>0.0412</v>
       </c>
       <c r="J423" t="n">
         <v>0</v>
       </c>
       <c r="K423" t="n">
-        <v>0.6019</v>
+        <v>0.6049</v>
       </c>
       <c r="L423" t="n">
         <v>0</v>
@@ -28008,7 +28008,7 @@
         </is>
       </c>
       <c r="F425" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="G425" t="inlineStr">
         <is>
@@ -28016,10 +28016,10 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="I425" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="J425" t="n">
         <v>0</v>
@@ -28138,7 +28138,7 @@
         </is>
       </c>
       <c r="F427" t="n">
-        <v>0.9673</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="G427" t="inlineStr">
         <is>
@@ -28149,13 +28149,13 @@
         <v>0</v>
       </c>
       <c r="I427" t="n">
-        <v>0.0327</v>
+        <v>0.0307</v>
       </c>
       <c r="J427" t="n">
         <v>0</v>
       </c>
       <c r="K427" t="n">
-        <v>0.9673</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="L427" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
         </is>
       </c>
       <c r="F430" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
@@ -28344,13 +28344,13 @@
         <v>0</v>
       </c>
       <c r="I430" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="J430" t="n">
         <v>0</v>
       </c>
       <c r="K430" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="L430" t="n">
         <v>0</v>
@@ -28528,7 +28528,7 @@
         </is>
       </c>
       <c r="F433" t="n">
-        <v>0.9976</v>
+        <v>0.9987</v>
       </c>
       <c r="G433" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>0.0024</v>
+        <v>0.0013</v>
       </c>
       <c r="I433" t="n">
         <v>0</v>
@@ -28545,7 +28545,7 @@
         <v>0</v>
       </c>
       <c r="K433" t="n">
-        <v>0.9976</v>
+        <v>0.9987</v>
       </c>
       <c r="L433" t="n">
         <v>0</v>
@@ -28788,7 +28788,7 @@
         </is>
       </c>
       <c r="F437" t="n">
-        <v>0.8741</v>
+        <v>0.8714</v>
       </c>
       <c r="G437" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>0.1259</v>
+        <v>0.1286</v>
       </c>
       <c r="I437" t="n">
         <v>0</v>
@@ -28805,7 +28805,7 @@
         <v>0</v>
       </c>
       <c r="K437" t="n">
-        <v>0.8741</v>
+        <v>0.8714</v>
       </c>
       <c r="L437" t="n">
         <v>0</v>
@@ -29113,7 +29113,7 @@
         </is>
       </c>
       <c r="F442" t="n">
-        <v>0.8788</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>0.8788</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="I442" t="n">
         <v>0</v>
@@ -29130,7 +29130,7 @@
         <v>0</v>
       </c>
       <c r="K442" t="n">
-        <v>0.1212</v>
+        <v>0.1154</v>
       </c>
       <c r="L442" t="n">
         <v>0</v>
@@ -29503,7 +29503,7 @@
         </is>
       </c>
       <c r="F448" t="n">
-        <v>0.9951</v>
+        <v>0.9952</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>0.0049</v>
+        <v>0.0048</v>
       </c>
       <c r="I448" t="n">
         <v>0</v>
@@ -29526,7 +29526,7 @@
         <v>0</v>
       </c>
       <c r="M448" t="n">
-        <v>0.9951</v>
+        <v>0.9952</v>
       </c>
       <c r="N448" t="n">
         <v>0</v>
@@ -29568,7 +29568,7 @@
         </is>
       </c>
       <c r="F449" t="n">
-        <v>0.9749</v>
+        <v>0.9748</v>
       </c>
       <c r="G449" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>0.0251</v>
+        <v>0.0252</v>
       </c>
       <c r="I449" t="n">
         <v>0</v>
@@ -29591,7 +29591,7 @@
         <v>0</v>
       </c>
       <c r="M449" t="n">
-        <v>0.9749</v>
+        <v>0.9748</v>
       </c>
       <c r="N449" t="n">
         <v>0</v>
@@ -29698,7 +29698,7 @@
         </is>
       </c>
       <c r="F451" t="n">
-        <v>0.96</v>
+        <v>0.9599</v>
       </c>
       <c r="G451" t="inlineStr">
         <is>
@@ -29706,16 +29706,16 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>0.0399</v>
+        <v>0.0401</v>
       </c>
       <c r="I451" t="n">
-        <v>0.96</v>
+        <v>0.9599</v>
       </c>
       <c r="J451" t="n">
         <v>0</v>
       </c>
       <c r="K451" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="L451" t="n">
         <v>0</v>
@@ -29828,7 +29828,7 @@
         </is>
       </c>
       <c r="F453" t="n">
-        <v>0.9992</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G453" t="inlineStr">
         <is>
@@ -29836,10 +29836,10 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>0.9992</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="I453" t="n">
-        <v>0.0008</v>
+        <v>0.0005</v>
       </c>
       <c r="J453" t="n">
         <v>0</v>
@@ -29958,7 +29958,7 @@
         </is>
       </c>
       <c r="F455" t="n">
-        <v>0.6227</v>
+        <v>0.6281</v>
       </c>
       <c r="G455" t="inlineStr">
         <is>
@@ -29966,10 +29966,10 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>0.3773</v>
+        <v>0.3719</v>
       </c>
       <c r="I455" t="n">
-        <v>0.6227</v>
+        <v>0.6281</v>
       </c>
       <c r="J455" t="n">
         <v>0</v>
@@ -30023,7 +30023,7 @@
         </is>
       </c>
       <c r="F456" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="I456" t="n">
         <v>0</v>
@@ -30040,7 +30040,7 @@
         <v>0</v>
       </c>
       <c r="K456" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="L456" t="n">
         <v>0</v>
@@ -30218,7 +30218,7 @@
         </is>
       </c>
       <c r="F459" t="n">
-        <v>0.9679</v>
+        <v>0.9675</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>0.0321</v>
+        <v>0.0325</v>
       </c>
       <c r="I459" t="n">
         <v>0</v>
@@ -30235,7 +30235,7 @@
         <v>0</v>
       </c>
       <c r="K459" t="n">
-        <v>0.9679</v>
+        <v>0.9675</v>
       </c>
       <c r="L459" t="n">
         <v>0</v>
@@ -30413,7 +30413,7 @@
         </is>
       </c>
       <c r="F462" t="n">
-        <v>0.5907</v>
+        <v>0.591</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
@@ -30424,13 +30424,13 @@
         <v>0</v>
       </c>
       <c r="I462" t="n">
-        <v>0.5907</v>
+        <v>0.591</v>
       </c>
       <c r="J462" t="n">
         <v>0</v>
       </c>
       <c r="K462" t="n">
-        <v>0.4093</v>
+        <v>0.409</v>
       </c>
       <c r="L462" t="n">
         <v>0</v>
@@ -30803,7 +30803,7 @@
         </is>
       </c>
       <c r="F468" t="n">
-        <v>0.9998</v>
+        <v>0.9993</v>
       </c>
       <c r="G468" t="inlineStr">
         <is>
@@ -30814,13 +30814,13 @@
         <v>0</v>
       </c>
       <c r="I468" t="n">
-        <v>0.0002</v>
+        <v>0.0007</v>
       </c>
       <c r="J468" t="n">
         <v>0</v>
       </c>
       <c r="K468" t="n">
-        <v>0.9998</v>
+        <v>0.9993</v>
       </c>
       <c r="L468" t="n">
         <v>0</v>
@@ -30933,7 +30933,7 @@
         </is>
       </c>
       <c r="F470" t="n">
-        <v>0.9978</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
@@ -30941,10 +30941,10 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>0.0022</v>
+        <v>0.0015</v>
       </c>
       <c r="I470" t="n">
-        <v>0.9978</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="J470" t="n">
         <v>0</v>
@@ -31063,7 +31063,7 @@
         </is>
       </c>
       <c r="F472" t="n">
-        <v>0.9786</v>
+        <v>0.9805</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
@@ -31074,13 +31074,13 @@
         <v>0</v>
       </c>
       <c r="I472" t="n">
-        <v>0.0214</v>
+        <v>0.0195</v>
       </c>
       <c r="J472" t="n">
         <v>0</v>
       </c>
       <c r="K472" t="n">
-        <v>0.9786</v>
+        <v>0.9805</v>
       </c>
       <c r="L472" t="n">
         <v>0</v>
@@ -31258,7 +31258,7 @@
         </is>
       </c>
       <c r="F475" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="G475" t="inlineStr">
         <is>
@@ -31266,10 +31266,10 @@
         </is>
       </c>
       <c r="H475" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="I475" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="J475" t="n">
         <v>0</v>
@@ -31453,7 +31453,7 @@
         </is>
       </c>
       <c r="F478" t="n">
-        <v>0.8763</v>
+        <v>0.883</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>0.8763</v>
+        <v>0.883</v>
       </c>
       <c r="I478" t="n">
         <v>0</v>
@@ -31470,7 +31470,7 @@
         <v>0</v>
       </c>
       <c r="K478" t="n">
-        <v>0.1237</v>
+        <v>0.117</v>
       </c>
       <c r="L478" t="n">
         <v>0</v>
@@ -31648,7 +31648,7 @@
         </is>
       </c>
       <c r="F481" t="n">
-        <v>0.9906</v>
+        <v>0.9919</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
@@ -31659,10 +31659,10 @@
         <v>0</v>
       </c>
       <c r="I481" t="n">
-        <v>0.0094</v>
+        <v>0.0081</v>
       </c>
       <c r="J481" t="n">
-        <v>0.9906</v>
+        <v>0.9919</v>
       </c>
       <c r="K481" t="n">
         <v>0</v>
@@ -31713,7 +31713,7 @@
         </is>
       </c>
       <c r="F482" t="n">
-        <v>0.9871</v>
+        <v>0.9873</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>0.0129</v>
+        <v>0.0127</v>
       </c>
       <c r="I482" t="n">
         <v>0</v>
@@ -31730,7 +31730,7 @@
         <v>0</v>
       </c>
       <c r="K482" t="n">
-        <v>0.9871</v>
+        <v>0.9873</v>
       </c>
       <c r="L482" t="n">
         <v>0</v>
@@ -31778,7 +31778,7 @@
         </is>
       </c>
       <c r="F483" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="G483" t="inlineStr">
         <is>
@@ -31789,13 +31789,13 @@
         <v>0</v>
       </c>
       <c r="I483" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="J483" t="n">
         <v>0</v>
       </c>
       <c r="K483" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="L483" t="n">
         <v>0</v>
@@ -31908,7 +31908,7 @@
         </is>
       </c>
       <c r="F485" t="n">
-        <v>0.6996</v>
+        <v>0.6894</v>
       </c>
       <c r="G485" t="inlineStr">
         <is>
@@ -31916,16 +31916,16 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>0.6996</v>
+        <v>0.6894</v>
       </c>
       <c r="I485" t="n">
-        <v>0.2847</v>
+        <v>0.2963</v>
       </c>
       <c r="J485" t="n">
         <v>0</v>
       </c>
       <c r="K485" t="n">
-        <v>0.0157</v>
+        <v>0.0143</v>
       </c>
       <c r="L485" t="n">
         <v>0</v>
@@ -32688,7 +32688,7 @@
         </is>
       </c>
       <c r="F497" t="n">
-        <v>0.615</v>
+        <v>0.6224</v>
       </c>
       <c r="G497" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         </is>
       </c>
       <c r="H497" t="n">
-        <v>0.385</v>
+        <v>0.3776</v>
       </c>
       <c r="I497" t="n">
         <v>0</v>
@@ -32705,7 +32705,7 @@
         <v>0</v>
       </c>
       <c r="K497" t="n">
-        <v>0.615</v>
+        <v>0.6224</v>
       </c>
       <c r="L497" t="n">
         <v>0</v>
@@ -32948,7 +32948,7 @@
         </is>
       </c>
       <c r="F501" t="n">
-        <v>0.9724</v>
+        <v>0.9711</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
@@ -32956,13 +32956,13 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>0.0276</v>
+        <v>0.0289</v>
       </c>
       <c r="I501" t="n">
         <v>0</v>
       </c>
       <c r="J501" t="n">
-        <v>0.9724</v>
+        <v>0.9711</v>
       </c>
       <c r="K501" t="n">
         <v>0</v>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="F509" t="n">
-        <v>0.9754</v>
+        <v>0.9775</v>
       </c>
       <c r="G509" t="inlineStr">
         <is>
@@ -33479,13 +33479,13 @@
         <v>0</v>
       </c>
       <c r="I509" t="n">
-        <v>0.0246</v>
+        <v>0.0225</v>
       </c>
       <c r="J509" t="n">
         <v>0</v>
       </c>
       <c r="K509" t="n">
-        <v>0.9754</v>
+        <v>0.9775</v>
       </c>
       <c r="L509" t="n">
         <v>0</v>
@@ -34114,7 +34114,7 @@
         </is>
       </c>
       <c r="F519" t="n">
-        <v>0.9974</v>
+        <v>0.9978</v>
       </c>
       <c r="G519" t="inlineStr">
         <is>
@@ -34122,16 +34122,16 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="I519" t="n">
-        <v>0.9974</v>
+        <v>0.9978</v>
       </c>
       <c r="J519" t="n">
         <v>0</v>
       </c>
       <c r="K519" t="n">
-        <v>0.0024</v>
+        <v>0.0022</v>
       </c>
       <c r="L519" t="n">
         <v>0</v>
@@ -34240,7 +34240,7 @@
         </is>
       </c>
       <c r="F521" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
@@ -34251,13 +34251,13 @@
         <v>0</v>
       </c>
       <c r="I521" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="J521" t="n">
         <v>0</v>
       </c>
       <c r="K521" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="L521" t="n">
         <v>0</v>
@@ -34305,7 +34305,7 @@
         </is>
       </c>
       <c r="F522" t="n">
-        <v>0.9214</v>
+        <v>0.922</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
@@ -34316,13 +34316,13 @@
         <v>0</v>
       </c>
       <c r="I522" t="n">
-        <v>0.9214</v>
+        <v>0.922</v>
       </c>
       <c r="J522" t="n">
         <v>0</v>
       </c>
       <c r="K522" t="n">
-        <v>0.0786</v>
+        <v>0.078</v>
       </c>
       <c r="L522" t="n">
         <v>0</v>
@@ -34370,7 +34370,7 @@
         </is>
       </c>
       <c r="F523" t="n">
-        <v>0.9973</v>
+        <v>0.9974</v>
       </c>
       <c r="G523" t="inlineStr">
         <is>
@@ -34381,13 +34381,13 @@
         <v>0</v>
       </c>
       <c r="I523" t="n">
-        <v>0.9973</v>
+        <v>0.9974</v>
       </c>
       <c r="J523" t="n">
         <v>0</v>
       </c>
       <c r="K523" t="n">
-        <v>0.0027</v>
+        <v>0.0026</v>
       </c>
       <c r="L523" t="n">
         <v>0</v>
@@ -34435,7 +34435,7 @@
         </is>
       </c>
       <c r="F524" t="n">
-        <v>0.9919</v>
+        <v>0.9903</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
@@ -34443,10 +34443,10 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>0.0081</v>
+        <v>0.0097</v>
       </c>
       <c r="I524" t="n">
-        <v>0.9919</v>
+        <v>0.9903</v>
       </c>
       <c r="J524" t="n">
         <v>0</v>
@@ -34565,7 +34565,7 @@
         </is>
       </c>
       <c r="F526" t="n">
-        <v>0.9992</v>
+        <v>0.9993</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>0.9992</v>
+        <v>0.9993</v>
       </c>
       <c r="I526" t="n">
         <v>0</v>
@@ -34582,7 +34582,7 @@
         <v>0</v>
       </c>
       <c r="K526" t="n">
-        <v>0.0008</v>
+        <v>0.0007</v>
       </c>
       <c r="L526" t="n">
         <v>0</v>
@@ -34695,7 +34695,7 @@
         </is>
       </c>
       <c r="F528" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
@@ -34706,10 +34706,10 @@
         <v>0</v>
       </c>
       <c r="I528" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="J528" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K528" t="n">
         <v>0</v>
@@ -34760,7 +34760,7 @@
         </is>
       </c>
       <c r="F529" t="n">
-        <v>0.9831</v>
+        <v>0.9847</v>
       </c>
       <c r="G529" t="inlineStr">
         <is>
@@ -34771,13 +34771,13 @@
         <v>0</v>
       </c>
       <c r="I529" t="n">
-        <v>0.9831</v>
+        <v>0.9847</v>
       </c>
       <c r="J529" t="n">
         <v>0</v>
       </c>
       <c r="K529" t="n">
-        <v>0.0169</v>
+        <v>0.0153</v>
       </c>
       <c r="L529" t="n">
         <v>0</v>
@@ -35215,7 +35215,7 @@
         </is>
       </c>
       <c r="F536" t="n">
-        <v>0.8466</v>
+        <v>0.8442</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
@@ -35223,16 +35223,16 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>0.1534</v>
+        <v>0.1557</v>
       </c>
       <c r="I536" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="J536" t="n">
         <v>0</v>
       </c>
       <c r="K536" t="n">
-        <v>0.8466</v>
+        <v>0.8442</v>
       </c>
       <c r="L536" t="n">
         <v>0</v>
@@ -35280,7 +35280,7 @@
         </is>
       </c>
       <c r="F537" t="n">
-        <v>0.8717</v>
+        <v>0.869</v>
       </c>
       <c r="G537" t="inlineStr">
         <is>
@@ -35288,16 +35288,16 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>0.0027</v>
+        <v>0.0033</v>
       </c>
       <c r="I537" t="n">
-        <v>0.8717</v>
+        <v>0.869</v>
       </c>
       <c r="J537" t="n">
         <v>0</v>
       </c>
       <c r="K537" t="n">
-        <v>0.1256</v>
+        <v>0.1277</v>
       </c>
       <c r="L537" t="n">
         <v>0</v>
@@ -35735,7 +35735,7 @@
         </is>
       </c>
       <c r="F544" t="n">
-        <v>0.6387</v>
+        <v>0.634</v>
       </c>
       <c r="G544" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         </is>
       </c>
       <c r="H544" t="n">
-        <v>0.6387</v>
+        <v>0.634</v>
       </c>
       <c r="I544" t="n">
         <v>0</v>
@@ -35752,7 +35752,7 @@
         <v>0</v>
       </c>
       <c r="K544" t="n">
-        <v>0.3613</v>
+        <v>0.366</v>
       </c>
       <c r="L544" t="n">
         <v>0</v>
@@ -35995,7 +35995,7 @@
         </is>
       </c>
       <c r="F548" t="n">
-        <v>0.9891</v>
+        <v>0.9888</v>
       </c>
       <c r="G548" t="inlineStr">
         <is>
@@ -36003,16 +36003,16 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>0.0109</v>
+        <v>0.0111</v>
       </c>
       <c r="I548" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="J548" t="n">
         <v>0</v>
       </c>
       <c r="K548" t="n">
-        <v>0.9891</v>
+        <v>0.9888</v>
       </c>
       <c r="L548" t="n">
         <v>0</v>
@@ -36125,7 +36125,7 @@
         </is>
       </c>
       <c r="F550" t="n">
-        <v>0.9691</v>
+        <v>0.9688</v>
       </c>
       <c r="G550" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>0.0309</v>
+        <v>0.0312</v>
       </c>
       <c r="I550" t="n">
         <v>0</v>
@@ -36142,7 +36142,7 @@
         <v>0</v>
       </c>
       <c r="K550" t="n">
-        <v>0.9691</v>
+        <v>0.9688</v>
       </c>
       <c r="L550" t="n">
         <v>0</v>
@@ -36190,7 +36190,7 @@
         </is>
       </c>
       <c r="F551" t="n">
-        <v>0.995</v>
+        <v>0.9961</v>
       </c>
       <c r="G551" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         </is>
       </c>
       <c r="H551" t="n">
-        <v>0.995</v>
+        <v>0.9961</v>
       </c>
       <c r="I551" t="n">
         <v>0</v>
@@ -36207,7 +36207,7 @@
         <v>0</v>
       </c>
       <c r="K551" t="n">
-        <v>0.005</v>
+        <v>0.0039</v>
       </c>
       <c r="L551" t="n">
         <v>0</v>
@@ -37226,7 +37226,7 @@
         </is>
       </c>
       <c r="F567" t="n">
-        <v>0.8843</v>
+        <v>0.8828</v>
       </c>
       <c r="G567" t="inlineStr">
         <is>
@@ -37237,13 +37237,13 @@
         <v>0</v>
       </c>
       <c r="I567" t="n">
-        <v>0.8843</v>
+        <v>0.8828</v>
       </c>
       <c r="J567" t="n">
         <v>0</v>
       </c>
       <c r="K567" t="n">
-        <v>0.1157</v>
+        <v>0.1172</v>
       </c>
       <c r="L567" t="n">
         <v>0</v>
@@ -37681,7 +37681,7 @@
         </is>
       </c>
       <c r="F574" t="n">
-        <v>0.9537</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="G574" t="inlineStr">
         <is>
@@ -37689,10 +37689,10 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>0.9537</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="I574" t="n">
-        <v>0.0463</v>
+        <v>0.0489</v>
       </c>
       <c r="J574" t="n">
         <v>0</v>
@@ -38136,7 +38136,7 @@
         </is>
       </c>
       <c r="F581" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.6313</v>
       </c>
       <c r="G581" t="inlineStr">
         <is>
@@ -38147,13 +38147,13 @@
         <v>0</v>
       </c>
       <c r="I581" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.6313</v>
       </c>
       <c r="J581" t="n">
         <v>0</v>
       </c>
       <c r="K581" t="n">
-        <v>0.3735</v>
+        <v>0.3687</v>
       </c>
       <c r="L581" t="n">
         <v>0</v>
@@ -39237,18 +39237,18 @@
         </is>
       </c>
       <c r="F598" t="n">
-        <v>0.9509</v>
+        <v>0.9494</v>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Safe Labour</t>
+          <t>Likely Labour</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>0.9509</v>
+        <v>0.9494</v>
       </c>
       <c r="I598" t="n">
-        <v>0.0491</v>
+        <v>0.0506</v>
       </c>
       <c r="J598" t="n">
         <v>0</v>
@@ -39432,7 +39432,7 @@
         </is>
       </c>
       <c r="F601" t="n">
-        <v>0.9966</v>
+        <v>0.9978</v>
       </c>
       <c r="G601" t="inlineStr">
         <is>
@@ -39440,7 +39440,7 @@
         </is>
       </c>
       <c r="H601" t="n">
-        <v>0.0034</v>
+        <v>0.0022</v>
       </c>
       <c r="I601" t="n">
         <v>0</v>
@@ -39449,7 +39449,7 @@
         <v>0</v>
       </c>
       <c r="K601" t="n">
-        <v>0.9966</v>
+        <v>0.9978</v>
       </c>
       <c r="L601" t="n">
         <v>0</v>
@@ -40277,7 +40277,7 @@
         </is>
       </c>
       <c r="F614" t="n">
-        <v>0.8256</v>
+        <v>0.8257</v>
       </c>
       <c r="G614" t="inlineStr">
         <is>
@@ -40285,10 +40285,10 @@
         </is>
       </c>
       <c r="H614" t="n">
-        <v>0.8256</v>
+        <v>0.8257</v>
       </c>
       <c r="I614" t="n">
-        <v>0.1744</v>
+        <v>0.1743</v>
       </c>
       <c r="J614" t="n">
         <v>0</v>
@@ -40342,7 +40342,7 @@
         </is>
       </c>
       <c r="F615" t="n">
-        <v>0.9999</v>
+        <v>0.9992</v>
       </c>
       <c r="G615" t="inlineStr">
         <is>
@@ -40353,7 +40353,7 @@
         <v>0</v>
       </c>
       <c r="I615" t="n">
-        <v>0.0001</v>
+        <v>0.0008</v>
       </c>
       <c r="J615" t="n">
         <v>0</v>
@@ -40365,7 +40365,7 @@
         <v>0</v>
       </c>
       <c r="M615" t="n">
-        <v>0.9999</v>
+        <v>0.9992</v>
       </c>
       <c r="N615" t="n">
         <v>0</v>
@@ -40403,11 +40403,11 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="F616" t="n">
-        <v>0.5001</v>
+        <v>0.5053</v>
       </c>
       <c r="G616" t="inlineStr">
         <is>
@@ -40415,7 +40415,7 @@
         </is>
       </c>
       <c r="H616" t="n">
-        <v>0.5001</v>
+        <v>0.4947</v>
       </c>
       <c r="I616" t="n">
         <v>0</v>
@@ -40424,7 +40424,7 @@
         <v>0</v>
       </c>
       <c r="K616" t="n">
-        <v>0.4999</v>
+        <v>0.5053</v>
       </c>
       <c r="L616" t="n">
         <v>0</v>
@@ -40537,7 +40537,7 @@
         </is>
       </c>
       <c r="F618" t="n">
-        <v>0.9327</v>
+        <v>0.9277</v>
       </c>
       <c r="G618" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         </is>
       </c>
       <c r="H618" t="n">
-        <v>0.0673</v>
+        <v>0.0723</v>
       </c>
       <c r="I618" t="n">
         <v>0</v>
@@ -40560,7 +40560,7 @@
         <v>0</v>
       </c>
       <c r="M618" t="n">
-        <v>0.9327</v>
+        <v>0.9277</v>
       </c>
       <c r="N618" t="n">
         <v>0</v>
@@ -40732,7 +40732,7 @@
         </is>
       </c>
       <c r="F621" t="n">
-        <v>0.6584</v>
+        <v>0.6631</v>
       </c>
       <c r="G621" t="inlineStr">
         <is>
@@ -40743,13 +40743,13 @@
         <v>0</v>
       </c>
       <c r="I621" t="n">
-        <v>0.6584</v>
+        <v>0.6631</v>
       </c>
       <c r="J621" t="n">
         <v>0</v>
       </c>
       <c r="K621" t="n">
-        <v>0.3416</v>
+        <v>0.3369</v>
       </c>
       <c r="L621" t="n">
         <v>0</v>
@@ -40988,7 +40988,7 @@
         </is>
       </c>
       <c r="F625" t="n">
-        <v>0.8552</v>
+        <v>0.8596</v>
       </c>
       <c r="G625" t="inlineStr">
         <is>
@@ -40996,16 +40996,16 @@
         </is>
       </c>
       <c r="H625" t="n">
-        <v>0.8552</v>
+        <v>0.8596</v>
       </c>
       <c r="I625" t="n">
-        <v>0.0012</v>
+        <v>0.0017</v>
       </c>
       <c r="J625" t="n">
         <v>0</v>
       </c>
       <c r="K625" t="n">
-        <v>0.1436</v>
+        <v>0.1387</v>
       </c>
       <c r="L625" t="n">
         <v>0</v>
@@ -41898,7 +41898,7 @@
         </is>
       </c>
       <c r="F639" t="n">
-        <v>0.9997</v>
+        <v>0.9998</v>
       </c>
       <c r="G639" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
         </is>
       </c>
       <c r="H639" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="I639" t="n">
         <v>0</v>
@@ -41915,7 +41915,7 @@
         <v>0</v>
       </c>
       <c r="K639" t="n">
-        <v>0.9997</v>
+        <v>0.9998</v>
       </c>
       <c r="L639" t="n">
         <v>0</v>
@@ -42093,7 +42093,7 @@
         </is>
       </c>
       <c r="F642" t="n">
-        <v>0.5216</v>
+        <v>0.5167</v>
       </c>
       <c r="G642" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         </is>
       </c>
       <c r="H642" t="n">
-        <v>0.5216</v>
+        <v>0.5167</v>
       </c>
       <c r="I642" t="n">
         <v>0</v>
@@ -42110,7 +42110,7 @@
         <v>0</v>
       </c>
       <c r="K642" t="n">
-        <v>0.4784</v>
+        <v>0.4833</v>
       </c>
       <c r="L642" t="n">
         <v>0</v>
@@ -42158,7 +42158,7 @@
         </is>
       </c>
       <c r="F643" t="n">
-        <v>0.9657</v>
+        <v>0.9629</v>
       </c>
       <c r="G643" t="inlineStr">
         <is>
@@ -42166,10 +42166,10 @@
         </is>
       </c>
       <c r="H643" t="n">
-        <v>0.9657</v>
+        <v>0.9629</v>
       </c>
       <c r="I643" t="n">
-        <v>0.0343</v>
+        <v>0.0371</v>
       </c>
       <c r="J643" t="n">
         <v>0</v>
@@ -42353,7 +42353,7 @@
         </is>
       </c>
       <c r="F646" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9993</v>
       </c>
       <c r="G646" t="inlineStr">
         <is>
@@ -42364,13 +42364,13 @@
         <v>0</v>
       </c>
       <c r="I646" t="n">
-        <v>0.0005</v>
+        <v>0.0007</v>
       </c>
       <c r="J646" t="n">
         <v>0</v>
       </c>
       <c r="K646" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9993</v>
       </c>
       <c r="L646" t="n">
         <v>0</v>
@@ -42825,10 +42825,10 @@
         <v>0.2114</v>
       </c>
       <c r="D3" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E3" t="n">
-        <v>118.1</v>
+        <v>118.2</v>
       </c>
       <c r="F3" t="n">
         <v>106</v>
@@ -42891,16 +42891,16 @@
         <v>0.2172</v>
       </c>
       <c r="D5" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E5" t="n">
-        <v>152.4</v>
+        <v>152.3</v>
       </c>
       <c r="F5" t="n">
         <v>141</v>
       </c>
       <c r="G5" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -42927,7 +42927,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -43538,7 +43538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E206"/>
+  <dimension ref="A1:E209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43596,7 +43596,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ashford</t>
+          <t>Amber Valley</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -43621,7 +43621,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amber Valley</t>
+          <t>Ashton-under-Lyne</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -43646,12 +43646,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ayr, Carrick and Cumnock</t>
+          <t>Ashford</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -43661,7 +43661,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -43671,12 +43671,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ashton-under-Lyne</t>
+          <t>Ayr, Carrick and Cumnock</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -43686,7 +43686,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -43696,7 +43696,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bassetlaw</t>
+          <t>Basildon and Billericay</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -43706,7 +43706,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -43721,7 +43721,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Basildon and Billericay</t>
+          <t>Barnsley South</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -43731,7 +43731,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -43771,7 +43771,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Barnsley South</t>
+          <t>Birmingham Erdington</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -43796,7 +43796,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bishop Auckland</t>
+          <t>Bassetlaw</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -43821,7 +43821,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Blackpool North and Fleetwood</t>
+          <t>Blyth and Ashington</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -43846,7 +43846,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Birmingham Northfield</t>
+          <t>Blaydon and Consett</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -43871,7 +43871,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Birmingham Erdington</t>
+          <t>Blackpool South</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -43896,12 +43896,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Glasgow South</t>
+          <t>Blackpool North and Fleetwood</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -43911,7 +43911,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -43921,7 +43921,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Erewash</t>
+          <t>Bishop Auckland</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -43946,7 +43946,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Farnham and Bordon</t>
+          <t>Birmingham Northfield</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -43956,12 +43956,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ld</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -43971,12 +43971,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Folkestone and Hythe</t>
+          <t>Glenrothes and Mid Fife</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -43986,7 +43986,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -43996,7 +43996,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Blackpool South</t>
+          <t>Forest of Dean</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -44011,7 +44011,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -44021,7 +44021,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Blaydon and Consett</t>
+          <t>Godalming and Ash</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -44031,12 +44031,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>ld</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -44046,12 +44046,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bolsover</t>
+          <t>Glasgow South</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -44061,7 +44061,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -44071,7 +44071,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Blyth and Ashington</t>
+          <t>Erewash</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -44096,12 +44096,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bradford South</t>
+          <t>Edinburgh South West</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -44111,7 +44111,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -44121,7 +44121,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Bolsover</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -44131,7 +44131,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -44171,7 +44171,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Bridgwater</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -44181,7 +44181,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -44196,7 +44196,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Brigg and Immingham</t>
+          <t>Bradford South</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -44206,7 +44206,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -44221,7 +44221,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bridlington and The Wolds</t>
+          <t>Chatham and Aylesford</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -44231,7 +44231,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -44246,7 +44246,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bridgwater</t>
+          <t>Cannock Chase</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -44256,7 +44256,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -44271,7 +44271,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Brentwood and Ongar</t>
+          <t>Burton and Uttoxeter</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -44281,7 +44281,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -44296,12 +44296,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Chatham and Aylesford</t>
+          <t>Caerphilly</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -44321,12 +44321,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Central Ayrshire</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -44336,7 +44336,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -44346,7 +44346,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Castle Point</t>
+          <t>Bridlington and The Wolds</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -44371,12 +44371,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Caerphilly</t>
+          <t>Central Ayrshire</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -44386,7 +44386,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -44396,7 +44396,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cannock Chase</t>
+          <t>Castle Point</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -44406,7 +44406,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -44421,12 +44421,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Burton and Uttoxeter</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -44436,7 +44436,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -44446,7 +44446,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Easington</t>
+          <t>Farnham and Bordon</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -44456,12 +44456,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>ld</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -44471,12 +44471,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>East Renfrewshire</t>
+          <t>Folkestone and Hythe</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -44486,7 +44486,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -44496,12 +44496,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Dover and Deal</t>
+          <t>East Renfrewshire</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -44511,7 +44511,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -44521,7 +44521,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dudley</t>
+          <t>Easington</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -44546,7 +44546,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Dumfries and Galloway</t>
+          <t>Edinburgh East and Musselburgh</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -44556,7 +44556,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -44571,22 +44571,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Doncaster East and the Isle of Axholme</t>
+          <t>Dumfries and Galloway</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -44596,7 +44596,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Derby South</t>
+          <t>Dudley</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -44621,7 +44621,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Derbyshire Dales</t>
+          <t>Doncaster East and the Isle of Axholme</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -44636,7 +44636,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -44646,7 +44646,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Doncaster Central</t>
+          <t>Dover and Deal</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -44671,12 +44671,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cumbernauld and Kirkintilloch</t>
+          <t>Doncaster Central</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -44686,7 +44686,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -44696,12 +44696,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Derbyshire Dales</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -44711,7 +44711,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -44721,12 +44721,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Edinburgh East and Musselburgh</t>
+          <t>Derby South</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -44736,7 +44736,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -44746,7 +44746,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Edinburgh South West</t>
+          <t>Cumbernauld and Kirkintilloch</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -44771,12 +44771,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Merthyr Tydfil and Aberdare</t>
+          <t>Makerfield</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -44796,7 +44796,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Newton Aycliffe and Spennymoor</t>
+          <t>Mansfield</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -44821,12 +44821,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Newcastle-under-Lyme</t>
+          <t>Merthyr Tydfil and Aberdare</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -44846,7 +44846,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Neath and Swansea East</t>
+          <t>Montgomeryshire and Glyndŵr</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -44871,12 +44871,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Montgomeryshire and Glyndŵr</t>
+          <t>Middlesbrough South and East Cleveland</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -44886,7 +44886,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -44896,22 +44896,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>North Antrim</t>
+          <t>Newton Aycliffe and Spennymoor</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Northern Ireland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ni_tuv</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ni_dup</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -44921,7 +44921,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Normanton and Hemsworth</t>
+          <t>Newcastle-under-Lyme</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -44946,7 +44946,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Llanelli</t>
+          <t>Neath and Swansea East</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -44971,12 +44971,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kingston upon Hull East</t>
+          <t>North Ayrshire and Arran</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -44986,7 +44986,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -44996,22 +44996,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Kingston upon Hull West and Haltemprice</t>
+          <t>North Antrim</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Northern Ireland</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>ni_tuv</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>ni_dup</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -45021,22 +45021,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Leigh and Atherton</t>
+          <t>North Down</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Northern Ireland</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>oth</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>ni_tuv</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -45046,12 +45046,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Normanton and Hemsworth</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -45061,7 +45061,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -45071,7 +45071,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Louth and Horncastle</t>
+          <t>North Somerset</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -45081,12 +45081,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>lab</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>con</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>reform</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -45096,7 +45096,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Hyndburn</t>
+          <t>Leigh and Atherton</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -45121,7 +45121,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Isle of Wight East</t>
+          <t>Kingston upon Hull West and Haltemprice</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -45131,7 +45131,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -45146,12 +45146,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kilmarnock and Loudoun</t>
+          <t>Lowestoft</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -45161,7 +45161,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -45196,12 +45196,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Heywood and Middleton North</t>
+          <t>Kilmarnock and Loudoun</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -45211,7 +45211,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -45221,7 +45221,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Hornchurch and Upminster</t>
+          <t>Kingston upon Hull East</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -45231,7 +45231,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -45246,7 +45246,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Houghton and Sunderland South</t>
+          <t>Louth and Horncastle</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -45256,7 +45256,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -45271,22 +45271,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Havant</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -45296,12 +45296,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Llanelli</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -45321,7 +45321,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Heywood and Middleton North</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -45346,7 +45346,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Hornchurch and Upminster</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -45356,7 +45356,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -45371,7 +45371,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Halesowen</t>
+          <t>Hyndburn</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -45396,7 +45396,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Great Grimsby and Cleethorpes</t>
+          <t>Houghton and Sunderland South</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -45421,22 +45421,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Gordon and Buchan</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -45446,7 +45446,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Godalming and Ash</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -45456,12 +45456,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ld</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -45471,12 +45471,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Glenrothes and Mid Fife</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -45486,7 +45486,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -45496,7 +45496,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Wolverhampton North East</t>
+          <t>Halesowen</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -45521,7 +45521,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Wellingborough and Rushden</t>
+          <t>Great Grimsby and Cleethorpes</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -45546,22 +45546,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Wigan</t>
+          <t>Gordon and Buchan</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -45571,7 +45571,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Washington and Gateshead South</t>
+          <t>Wolverhampton North East</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -45596,7 +45596,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Warrington North</t>
+          <t>Wigan</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -45621,7 +45621,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Walsall and Bloxwich</t>
+          <t>Washington and Gateshead South</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -45646,7 +45646,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Spen Valley</t>
+          <t>Wellingborough and Rushden</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -45671,7 +45671,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>South West Norfolk</t>
+          <t>Warrington North</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -45696,12 +45696,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Stirling and Strathallan</t>
+          <t>Telford</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -45711,7 +45711,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -45721,7 +45721,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Stockton North</t>
+          <t>Spen Valley</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -45746,7 +45746,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Stoke-on-Trent Central</t>
+          <t>St Austell and Newquay</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -45771,7 +45771,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Stoke-on-Trent North</t>
+          <t>Staffordshire Moorlands</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -45781,7 +45781,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -45796,12 +45796,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>St Austell and Newquay</t>
+          <t>Stirling and Strathallan</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -45811,7 +45811,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -45821,7 +45821,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Staffordshire Moorlands</t>
+          <t>Stoke-on-Trent North</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -45831,7 +45831,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -45846,7 +45846,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Telford</t>
+          <t>Stoke-on-Trent South</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -45871,12 +45871,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tamworth</t>
+          <t>Torfaen</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -45896,7 +45896,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Rotherham</t>
+          <t>Tipton and Wednesbury</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -45921,7 +45921,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Rother Valley</t>
+          <t>Thurrock</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -45946,7 +45946,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Sittingbourne and Sheppey</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -45996,7 +45996,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>South East Cornwall</t>
+          <t>Rotherham</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -46021,7 +46021,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>South Derbyshire</t>
+          <t>Sherwood Forest</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -46046,7 +46046,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sittingbourne and Sheppey</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -46071,7 +46071,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sherwood Forest</t>
+          <t>South West Norfolk</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -46121,7 +46121,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Redcar</t>
+          <t>South Derbyshire</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -46146,12 +46146,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Rochester and Strood</t>
+          <t>Rhondda and Ogmore</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -46171,12 +46171,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Rhondda and Ogmore</t>
+          <t>Redcar</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -46196,7 +46196,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Rawmarsh and Conisbrough</t>
+          <t>Rochester and Strood</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46221,7 +46221,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Mansfield</t>
+          <t>Ribble Valley</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -46246,7 +46246,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Makerfield</t>
+          <t>Rawmarsh and Conisbrough</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -46271,7 +46271,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Lowestoft</t>
+          <t>Poole</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -46286,7 +46286,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -46296,7 +46296,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Nuneaton</t>
+          <t>Pontefract, Castleford and Knottingley</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -46321,7 +46321,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ossett and Denby Dale</t>
+          <t>Plymouth Moor View</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -46346,12 +46346,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>North Ayrshire and Arran</t>
+          <t>Penistone and Stocksbridge</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -46361,7 +46361,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -46371,7 +46371,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Oldham East and Saddleworth</t>
+          <t>Nuneaton</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -46396,7 +46396,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>North West Leicestershire</t>
+          <t>Ossett and Denby Dale</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -46421,7 +46421,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>North Warwickshire and Bedworth</t>
+          <t>Oldham East and Saddleworth</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -46471,22 +46471,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>North Down</t>
+          <t>North East Hertfordshire</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Northern Ireland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>oth</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ni_tuv</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -46496,7 +46496,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Stoke-on-Trent South</t>
+          <t>North Warwickshire and Bedworth</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -46521,7 +46521,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Stourbridge</t>
+          <t>Stoke-on-Trent Central</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -46546,7 +46546,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sunderland Central</t>
+          <t>Stockton North</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -46571,12 +46571,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Torfaen</t>
+          <t>Stourbridge</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -46596,7 +46596,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Tipton and Wednesbury</t>
+          <t>Sunderland Central</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -46621,7 +46621,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Thurrock</t>
+          <t>Tamworth</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -46646,7 +46646,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Pontefract, Castleford and Knottingley</t>
+          <t>Walsall and Bloxwich</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -46671,7 +46671,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Penistone and Stocksbridge</t>
+          <t>South East Cornwall</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -46690,13 +46690,13 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Poole</t>
+          <t>Isle of Wight East</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -46706,22 +46706,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Middlesbrough South and East Cleveland</t>
+          <t>Rother Valley</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -46736,7 +46736,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -46746,7 +46746,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>West Aberdeenshire and Kincardine</t>
+          <t>Glasgow South West</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -46756,7 +46756,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -46771,7 +46771,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Birmingham Hall Green and Moseley</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -46781,12 +46781,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>oth</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -46796,7 +46796,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Forest of Dean</t>
+          <t>Wolverhampton South East</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -46811,17 +46811,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Plymouth Moor View</t>
+          <t>Havant</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -46831,7 +46831,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -46840,13 +46840,13 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.9999</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>North Somerset</t>
+          <t>Gillingham and Rainham</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -46861,22 +46861,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.9998</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Ribble Valley</t>
+          <t>Alyn and Deeside</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -46886,17 +46886,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.9998</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Rayleigh and Wickford</t>
+          <t>Birmingham Hall Green and Moseley</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -46906,22 +46906,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>oth</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.9998</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Wolverhampton South East</t>
+          <t>Brigg and Immingham</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -46931,7 +46931,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -46940,13 +46940,13 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.9997</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>North East Hertfordshire</t>
+          <t>North West Leicestershire</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -46961,32 +46961,32 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9996</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Glasgow South West</t>
+          <t>Brentwood and Ongar</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -46996,12 +46996,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Alyn and Deeside</t>
+          <t>Birmingham Hodge Hill and Solihull North</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -47015,13 +47015,13 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9993</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Gillingham and Rainham</t>
+          <t>Wyre Forest</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -47031,7 +47031,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -47040,13 +47040,13 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9993</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Wyre Forest</t>
+          <t>Rayleigh and Wickford</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -47065,38 +47065,38 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9993</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Birmingham Hodge Hill and Solihull North</t>
+          <t>West Aberdeenshire and Kincardine</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.999</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Aldridge-Brownhills</t>
+          <t>Northampton South</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -47106,7 +47106,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -47115,7 +47115,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.9986</v>
+        <v>0.9987</v>
       </c>
     </row>
     <row r="144">
@@ -47140,13 +47140,13 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9978</v>
+        <v>0.9985000000000001</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Northampton South</t>
+          <t>Aldridge-Brownhills</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -47156,7 +47156,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -47165,18 +47165,18 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9976</v>
+        <v>0.9985000000000001</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>South Dorset</t>
+          <t>Glasgow East</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -47186,22 +47186,22 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.9974</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Glasgow East</t>
+          <t>Wakefield and Rothwell</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -47211,17 +47211,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.9969</v>
+        <v>0.9978</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Wakefield and Rothwell</t>
+          <t>South Dorset</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -47236,11 +47236,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.9966</v>
+        <v>0.9978</v>
       </c>
     </row>
     <row r="149">
@@ -47265,13 +47265,13 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.996</v>
+        <v>0.9973</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Bracknell</t>
+          <t>Bolton South and Walkden</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -47286,17 +47286,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.9959</v>
+        <v>0.9966</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Bolton South and Walkden</t>
+          <t>Bracknell</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -47311,11 +47311,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.9953</v>
+        <v>0.9954</v>
       </c>
     </row>
     <row r="152">
@@ -47340,7 +47340,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.9951</v>
+        <v>0.9952</v>
       </c>
     </row>
     <row r="153">
@@ -47365,7 +47365,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.9928</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="154">
@@ -47390,13 +47390,13 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.9921</v>
+        <v>0.9928</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>South Norfolk</t>
+          <t>Romsey and Southampton North</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -47406,12 +47406,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>ld</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -47421,12 +47421,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>North East Derbyshire</t>
+          <t>Newport West and Islwyn</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -47436,17 +47436,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.9918</v>
+        <v>0.9913</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Romsey and Southampton North</t>
+          <t>South Norfolk</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -47456,27 +47456,27 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
+          <t>lab</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
           <t>con</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>ld</t>
-        </is>
-      </c>
       <c r="E157" t="n">
-        <v>0.9906</v>
+        <v>0.9903</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Newport West and Islwyn</t>
+          <t>North East Derbyshire</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -47486,11 +47486,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>reform</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.9903</v>
       </c>
     </row>
     <row r="159">
@@ -47515,13 +47515,13 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.9903</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Stafford</t>
+          <t>Kettering</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -47540,13 +47540,13 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.9891</v>
+        <v>0.9898</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Kettering</t>
+          <t>Stafford</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -47565,7 +47565,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.989</v>
+        <v>0.9888</v>
       </c>
     </row>
     <row r="162">
@@ -47590,7 +47590,7 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.9871</v>
+        <v>0.9873</v>
       </c>
     </row>
     <row r="163">
@@ -47615,13 +47615,13 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9849</v>
+        <v>0.9863</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Carlisle</t>
+          <t>Middlesbrough and Thornaby East</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -47640,13 +47640,13 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.9822</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Middlesbrough and Thornaby East</t>
+          <t>Carlisle</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -47665,7 +47665,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9821</v>
+        <v>0.9817</v>
       </c>
     </row>
     <row r="166">
@@ -47690,7 +47690,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.9786</v>
+        <v>0.9805</v>
       </c>
     </row>
     <row r="167">
@@ -47715,7 +47715,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.9754</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="168">
@@ -47740,7 +47740,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9749</v>
+        <v>0.9748</v>
       </c>
     </row>
     <row r="169">
@@ -47765,13 +47765,13 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9724</v>
+        <v>0.9711</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Stalybridge and Hyde</t>
+          <t>North West Cambridgeshire</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -47790,13 +47790,13 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.9691</v>
+        <v>0.9693000000000001</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Broxtowe</t>
+          <t>Stalybridge and Hyde</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -47815,18 +47815,18 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9691</v>
+        <v>0.9688</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Pontypridd</t>
+          <t>Broxtowe</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -47840,18 +47840,18 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9679</v>
+        <v>0.9681999999999999</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>North West Cambridgeshire</t>
+          <t>Pontypridd</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -47865,7 +47865,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>0.9673</v>
+        <v>0.9675</v>
       </c>
     </row>
     <row r="174">
@@ -47890,7 +47890,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>0.9644</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="175">
@@ -47915,7 +47915,7 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>0.96</v>
+        <v>0.9599</v>
       </c>
     </row>
     <row r="176">
@@ -47940,7 +47940,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0.954</v>
+        <v>0.9523</v>
       </c>
     </row>
     <row r="177">
@@ -47965,7 +47965,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>0.9493</v>
+        <v>0.9468</v>
       </c>
     </row>
     <row r="178">
@@ -47990,7 +47990,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>0.9374</v>
+        <v>0.9351</v>
       </c>
     </row>
     <row r="179">
@@ -48015,7 +48015,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>0.9327</v>
+        <v>0.9277</v>
       </c>
     </row>
     <row r="180">
@@ -48065,7 +48065,7 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.9213</v>
       </c>
     </row>
     <row r="182">
@@ -48090,7 +48090,7 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>0.9129</v>
+        <v>0.9137999999999999</v>
       </c>
     </row>
     <row r="183">
@@ -48115,7 +48115,7 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>0.8957000000000001</v>
+        <v>0.8942</v>
       </c>
     </row>
     <row r="184">
@@ -48140,7 +48140,7 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8891</v>
       </c>
     </row>
     <row r="185">
@@ -48165,7 +48165,7 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>0.8868</v>
+        <v>0.8867</v>
       </c>
     </row>
     <row r="186">
@@ -48190,7 +48190,7 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>0.8843</v>
+        <v>0.8828</v>
       </c>
     </row>
     <row r="187">
@@ -48215,7 +48215,7 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>0.8741</v>
+        <v>0.8714</v>
       </c>
     </row>
     <row r="188">
@@ -48240,7 +48240,7 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>0.8717</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="189">
@@ -48265,7 +48265,7 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>0.8466</v>
+        <v>0.8442</v>
       </c>
     </row>
     <row r="190">
@@ -48290,7 +48290,7 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>0.8257</v>
+        <v>0.8269</v>
       </c>
     </row>
     <row r="191">
@@ -48315,13 +48315,13 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>0.8124</v>
+        <v>0.8119</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Harwich and North Essex</t>
+          <t>Bexleyheath and Crayford</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -48331,7 +48331,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -48340,13 +48340,13 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>0.7814</v>
+        <v>0.7813</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Bexleyheath and Crayford</t>
+          <t>Harwich and North Essex</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -48356,7 +48356,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -48365,18 +48365,18 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>0.7768</v>
+        <v>0.7788</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Hexham</t>
+          <t>Edinburgh North and Leith</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -48386,22 +48386,22 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>snp</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>0.7645</v>
+        <v>0.7635</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Edinburgh North and Leith</t>
+          <t>Hexham</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -48411,11 +48411,11 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>snp</t>
+          <t>con</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>0.763</v>
+        <v>0.7625</v>
       </c>
     </row>
     <row r="196">
@@ -48440,7 +48440,7 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>0.7446</v>
+        <v>0.7477</v>
       </c>
     </row>
     <row r="197">
@@ -48465,7 +48465,7 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6892</v>
       </c>
     </row>
     <row r="198">
@@ -48490,7 +48490,7 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>0.6459</v>
+        <v>0.6428</v>
       </c>
     </row>
     <row r="199">
@@ -48515,7 +48515,7 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>0.6227</v>
+        <v>0.6281</v>
       </c>
     </row>
     <row r="200">
@@ -48540,7 +48540,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>0.615</v>
+        <v>0.6224</v>
       </c>
     </row>
     <row r="201">
@@ -48565,13 +48565,13 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>0.6019</v>
+        <v>0.6049</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Gainsborough</t>
+          <t>Portsmouth North</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -48581,22 +48581,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
+          <t>lab</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
           <t>con</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>reform</t>
-        </is>
-      </c>
       <c r="E202" t="n">
-        <v>0.5938</v>
+        <v>0.591</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Portsmouth North</t>
+          <t>Gainsborough</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -48606,16 +48606,16 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>con</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>con</t>
+          <t>reform</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>0.5907</v>
+        <v>0.5846</v>
       </c>
     </row>
     <row r="204">
@@ -48640,7 +48640,7 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.5836</v>
       </c>
     </row>
     <row r="205">
@@ -48665,7 +48665,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5591</v>
       </c>
     </row>
     <row r="206">
@@ -48690,7 +48690,82 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>0.5284</v>
+        <v>0.5375</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>West Bromwich</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>lab</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>reform</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>0.5053</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Bridgend</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Wales</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>lab</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>reform</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>0.5026</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Gravesham</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>lab</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>con</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>0.3977</v>
       </c>
     </row>
   </sheetData>
